--- a/data/trans_camb/P1801_2016_2023-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1801_2016_2023-Estudios-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>-1,51</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-1,43</t>
+          <t>-1,47</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>-1,34</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 6,56</t>
+          <t>-6,72; 3,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 3,04</t>
+          <t>-5,52; 2,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 3,4</t>
+          <t>-4,5; 2,26</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>-2,63%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-2,18%</t>
+          <t>-2,24%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>-2,16%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 12,0</t>
+          <t>-11,1; 7,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 4,8</t>
+          <t>-8,08; 4,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 5,66</t>
+          <t>-7,08; 3,82</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,29</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>-2,58</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>-0,92</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 20,08</t>
+          <t>-2,46; 4,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 12,79</t>
+          <t>-5,54; 0,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 13,83</t>
+          <t>-3,11; 1,27</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-0,09%</t>
+          <t>-4,8%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>-1,9%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 47,57</t>
+          <t>-5,59; 9,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 24,71</t>
+          <t>-10,01; 0,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 28,79</t>
+          <t>-6,28; 2,65</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13,13</t>
+          <t>11,39</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,16</t>
+          <t>6,52</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,66</t>
+          <t>8,99</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,87; 19,19</t>
+          <t>5,29; 17,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 11,34</t>
+          <t>0,82; 11,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 13,77</t>
+          <t>4,6; 13,11</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,06; 50,26</t>
+          <t>11,9; 45,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 22,32</t>
+          <t>1,44; 22,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,96; 30,29</t>
+          <t>9,08; 28,14</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,47</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>-1,27</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 17,5</t>
+          <t>-0,68; 4,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 7,73</t>
+          <t>-3,77; 0,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 9,29</t>
+          <t>-1,51; 1,86</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-0,17%</t>
+          <t>-2,22%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,64; 38,11</t>
+          <t>-1,53; 9,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 13,7</t>
+          <t>-6,45; 1,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 17,95</t>
+          <t>-2,87; 3,61</t>
         </is>
       </c>
     </row>
